--- a/2d/results/best_unet_nofilter_projection_mean/best_unet.xlsx
+++ b/2d/results/best_unet_nofilter_projection_mean/best_unet.xlsx
@@ -535,55 +535,55 @@
         <v>140</v>
       </c>
       <c r="C2" t="n">
-        <v>10.7235012383579</v>
+        <v>17.1913880048285</v>
       </c>
       <c r="D2" t="n">
-        <v>17.19139282541193</v>
+        <v>10.72350320971258</v>
       </c>
       <c r="E2" t="n">
-        <v>23.67550763345644</v>
+        <v>23.67551765644586</v>
       </c>
       <c r="F2" t="n">
-        <v>13.06542985351978</v>
+        <v>13.06543127443302</v>
       </c>
       <c r="G2" t="n">
-        <v>9.968000437172051</v>
+        <v>9.968000241789925</v>
       </c>
       <c r="H2" t="n">
-        <v>75.67025641154764</v>
+        <v>75.6702603357684</v>
       </c>
       <c r="I2" t="n">
-        <v>73.45984204692255</v>
+        <v>73.45984220576507</v>
       </c>
       <c r="J2" t="n">
-        <v>62.45795206174887</v>
+        <v>62.45796007680266</v>
       </c>
       <c r="K2" t="n">
-        <v>61.91008550703485</v>
+        <v>61.91008622428454</v>
       </c>
       <c r="L2" t="n">
-        <v>37.7582453727631</v>
+        <v>37.75824382840262</v>
       </c>
       <c r="M2" t="n">
-        <v>29.3170966022389</v>
+        <v>29.31709498830734</v>
       </c>
       <c r="N2" t="n">
-        <v>72.1350546380235</v>
+        <v>72.13506012522207</v>
       </c>
       <c r="O2" t="n">
-        <v>59.73435250608468</v>
+        <v>59.73434710318713</v>
       </c>
       <c r="P2" t="n">
-        <v>17.42470773176312</v>
+        <v>17.42470085273971</v>
       </c>
       <c r="Q2" t="n">
-        <v>16.59394310648646</v>
+        <v>16.59393930612883</v>
       </c>
       <c r="R2" t="n">
-        <v>15.7273630872476</v>
+        <v>15.72736227004281</v>
       </c>
       <c r="S2" t="n">
-        <v>17.1706321457525</v>
+        <v>17.1706454952099</v>
       </c>
     </row>
     <row r="3">
@@ -596,55 +596,55 @@
         <v>141</v>
       </c>
       <c r="C3" t="n">
-        <v>6.391210832973282</v>
+        <v>12.37436192103275</v>
       </c>
       <c r="D3" t="n">
-        <v>12.37435462553526</v>
+        <v>6.39121034849195</v>
       </c>
       <c r="E3" t="n">
-        <v>25.27683113330966</v>
+        <v>25.27682963516356</v>
       </c>
       <c r="F3" t="n">
-        <v>21.15501295273826</v>
+        <v>21.1550117547425</v>
       </c>
       <c r="G3" t="n">
-        <v>15.80365518460297</v>
+        <v>15.80365461591601</v>
       </c>
       <c r="H3" t="n">
-        <v>81.37442718452471</v>
+        <v>81.37442592849129</v>
       </c>
       <c r="I3" t="n">
-        <v>88.02659673576785</v>
+        <v>88.02658995922096</v>
       </c>
       <c r="J3" t="n">
-        <v>70.50999389345527</v>
+        <v>70.50998324251277</v>
       </c>
       <c r="K3" t="n">
-        <v>76.9391505016218</v>
+        <v>76.93915156275423</v>
       </c>
       <c r="L3" t="n">
-        <v>53.61702817070257</v>
+        <v>53.61703105952269</v>
       </c>
       <c r="M3" t="n">
-        <v>44.10075331987967</v>
+        <v>44.10075824345201</v>
       </c>
       <c r="N3" t="n">
-        <v>80.46903770425789</v>
+        <v>80.46903373757819</v>
       </c>
       <c r="O3" t="n">
-        <v>70.48574674909112</v>
+        <v>70.48574316789333</v>
       </c>
       <c r="P3" t="n">
-        <v>13.35021144246726</v>
+        <v>13.35022323333284</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.96207455558787</v>
+        <v>12.96207614962903</v>
       </c>
       <c r="R3" t="n">
-        <v>12.59684390290954</v>
+        <v>12.59683606381701</v>
       </c>
       <c r="S3" t="n">
-        <v>12.41114482085422</v>
+        <v>12.41114498237569</v>
       </c>
     </row>
     <row r="4">
@@ -657,55 +657,55 @@
         <v>149</v>
       </c>
       <c r="C4" t="n">
-        <v>7.999022360196093</v>
+        <v>9.408123224513668</v>
       </c>
       <c r="D4" t="n">
-        <v>9.408123522055597</v>
+        <v>7.999021292500264</v>
       </c>
       <c r="E4" t="n">
-        <v>17.04207619019282</v>
+        <v>17.04209245603023</v>
       </c>
       <c r="F4" t="n">
-        <v>11.13812464063109</v>
+        <v>11.1381249721468</v>
       </c>
       <c r="G4" t="n">
-        <v>9.240036281640059</v>
+        <v>9.240034732448599</v>
       </c>
       <c r="H4" t="n">
-        <v>82.98990964894755</v>
+        <v>82.9899126568486</v>
       </c>
       <c r="I4" t="n">
-        <v>74.41229264485243</v>
+        <v>74.41229767416432</v>
       </c>
       <c r="J4" t="n">
-        <v>71.41829992274732</v>
+        <v>71.41829996058893</v>
       </c>
       <c r="K4" t="n">
-        <v>63.2487569581098</v>
+        <v>63.24876618357676</v>
       </c>
       <c r="L4" t="n">
-        <v>33.29506849053596</v>
+        <v>33.29506958996561</v>
       </c>
       <c r="M4" t="n">
-        <v>26.89594255928599</v>
+        <v>26.89594004564418</v>
       </c>
       <c r="N4" t="n">
-        <v>77.43167280579262</v>
+        <v>77.43168118873314</v>
       </c>
       <c r="O4" t="n">
-        <v>65.93783814523033</v>
+        <v>65.93784011197602</v>
       </c>
       <c r="P4" t="n">
-        <v>13.93797035741805</v>
+        <v>13.93797354934514</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.43901637081372</v>
+        <v>14.43901475691114</v>
       </c>
       <c r="R4" t="n">
-        <v>15.00422213037421</v>
+        <v>15.00421505810901</v>
       </c>
       <c r="S4" t="n">
-        <v>14.84276318974967</v>
+        <v>14.84276964400785</v>
       </c>
     </row>
     <row r="5">
@@ -718,55 +718,55 @@
         <v>160</v>
       </c>
       <c r="C5" t="n">
-        <v>11.51882265502704</v>
+        <v>15.9012155646825</v>
       </c>
       <c r="D5" t="n">
-        <v>15.90121355833132</v>
+        <v>11.51883286635027</v>
       </c>
       <c r="E5" t="n">
-        <v>33.21205165949994</v>
+        <v>33.21206386674271</v>
       </c>
       <c r="F5" t="n">
-        <v>10.94531240026319</v>
+        <v>10.94531196145207</v>
       </c>
       <c r="G5" t="n">
-        <v>7.309737262718727</v>
+        <v>7.309735806694785</v>
       </c>
       <c r="H5" t="n">
-        <v>68.24729892412819</v>
+        <v>68.24729665178604</v>
       </c>
       <c r="I5" t="n">
-        <v>67.40727876173806</v>
+        <v>67.40729494083915</v>
       </c>
       <c r="J5" t="n">
-        <v>53.69306746391476</v>
+        <v>53.69306056156531</v>
       </c>
       <c r="K5" t="n">
-        <v>51.74053428505132</v>
+        <v>51.74052789194971</v>
       </c>
       <c r="L5" t="n">
-        <v>35.3743261260249</v>
+        <v>35.37432263664697</v>
       </c>
       <c r="M5" t="n">
-        <v>28.11253892276619</v>
+        <v>28.11253471873947</v>
       </c>
       <c r="N5" t="n">
-        <v>65.69059848179369</v>
+        <v>65.69060219892286</v>
       </c>
       <c r="O5" t="n">
-        <v>50.71337368345679</v>
+        <v>50.71336807284813</v>
       </c>
       <c r="P5" t="n">
-        <v>21.28816568109123</v>
+        <v>21.28817285813567</v>
       </c>
       <c r="Q5" t="n">
-        <v>22.26541417885824</v>
+        <v>22.26543173992862</v>
       </c>
       <c r="R5" t="n">
-        <v>23.24621109666975</v>
+        <v>23.24623892697194</v>
       </c>
       <c r="S5" t="n">
-        <v>22.77959790402643</v>
+        <v>22.77961038272962</v>
       </c>
     </row>
     <row r="6">
@@ -779,55 +779,55 @@
         <v>170</v>
       </c>
       <c r="C6" t="n">
-        <v>8.837925312113047</v>
+        <v>14.59153886933953</v>
       </c>
       <c r="D6" t="n">
-        <v>14.59154045123365</v>
+        <v>8.837936138548233</v>
       </c>
       <c r="E6" t="n">
-        <v>23.95293814992619</v>
+        <v>23.95294242439894</v>
       </c>
       <c r="F6" t="n">
-        <v>14.84331727417465</v>
+        <v>14.84331724861455</v>
       </c>
       <c r="G6" t="n">
-        <v>11.28333936585354</v>
+        <v>11.28333873067911</v>
       </c>
       <c r="H6" t="n">
-        <v>80.03329687091511</v>
+        <v>80.03329544047475</v>
       </c>
       <c r="I6" t="n">
-        <v>75.55600934107801</v>
+        <v>75.55599936287534</v>
       </c>
       <c r="J6" t="n">
-        <v>57.02504264852544</v>
+        <v>57.02504921161473</v>
       </c>
       <c r="K6" t="n">
-        <v>61.74427357748833</v>
+        <v>61.74427003876174</v>
       </c>
       <c r="L6" t="n">
-        <v>42.41044330820009</v>
+        <v>42.41043470816869</v>
       </c>
       <c r="M6" t="n">
-        <v>37.10195777077783</v>
+        <v>37.10194994405313</v>
       </c>
       <c r="N6" t="n">
-        <v>74.81928197908394</v>
+        <v>74.81926628599307</v>
       </c>
       <c r="O6" t="n">
-        <v>55.83458978044327</v>
+        <v>55.83459187601648</v>
       </c>
       <c r="P6" t="n">
-        <v>28.751574062686</v>
+        <v>28.7515645233392</v>
       </c>
       <c r="Q6" t="n">
-        <v>23.66680467477309</v>
+        <v>23.66679705792902</v>
       </c>
       <c r="R6" t="n">
-        <v>18.28050284196415</v>
+        <v>18.28049657379685</v>
       </c>
       <c r="S6" t="n">
-        <v>25.37197988255333</v>
+        <v>25.37196114117926</v>
       </c>
     </row>
     <row r="7">
@@ -840,55 +840,55 @@
         <v>184</v>
       </c>
       <c r="C7" t="n">
-        <v>10.19025977735071</v>
+        <v>12.34960640984924</v>
       </c>
       <c r="D7" t="n">
-        <v>12.34960223900311</v>
+        <v>10.19025612983872</v>
       </c>
       <c r="E7" t="n">
-        <v>25.6318034327737</v>
+        <v>25.63177835798014</v>
       </c>
       <c r="F7" t="n">
-        <v>12.52307333890363</v>
+        <v>12.52307031037853</v>
       </c>
       <c r="G7" t="n">
-        <v>9.312787955609167</v>
+        <v>9.312788848645738</v>
       </c>
       <c r="H7" t="n">
-        <v>77.58726717796009</v>
+        <v>77.58726735950572</v>
       </c>
       <c r="I7" t="n">
-        <v>73.94794279748322</v>
+        <v>73.94793078992159</v>
       </c>
       <c r="J7" t="n">
-        <v>65.37255711664477</v>
+        <v>65.37255970879188</v>
       </c>
       <c r="K7" t="n">
-        <v>62.56229635097838</v>
+        <v>62.56229207113487</v>
       </c>
       <c r="L7" t="n">
-        <v>35.04506550610368</v>
+        <v>35.04506141651712</v>
       </c>
       <c r="M7" t="n">
-        <v>28.27915121968275</v>
+        <v>28.27914684212428</v>
       </c>
       <c r="N7" t="n">
-        <v>73.36883059131856</v>
+        <v>73.36882814481218</v>
       </c>
       <c r="O7" t="n">
-        <v>62.56059003245958</v>
+        <v>62.5605882042253</v>
       </c>
       <c r="P7" t="n">
-        <v>15.63039187388693</v>
+        <v>15.6303887171547</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.53419570178406</v>
+        <v>15.53419022595013</v>
       </c>
       <c r="R7" t="n">
-        <v>15.40458502784492</v>
+        <v>15.40457705660049</v>
       </c>
       <c r="S7" t="n">
-        <v>14.68329544940967</v>
+        <v>14.68329486124664</v>
       </c>
     </row>
     <row r="8">
@@ -901,55 +901,55 @@
         <v>190</v>
       </c>
       <c r="C8" t="n">
-        <v>4.884873973186092</v>
+        <v>11.50388386090963</v>
       </c>
       <c r="D8" t="n">
-        <v>11.50388930871032</v>
+        <v>4.884867107617458</v>
       </c>
       <c r="E8" t="n">
-        <v>34.40662626456077</v>
+        <v>34.40661891430317</v>
       </c>
       <c r="F8" t="n">
-        <v>17.373082732574</v>
+        <v>17.37308260205274</v>
       </c>
       <c r="G8" t="n">
-        <v>11.3955489943955</v>
+        <v>11.39555018900475</v>
       </c>
       <c r="H8" t="n">
-        <v>97.50695701812936</v>
+        <v>97.50697397206069</v>
       </c>
       <c r="I8" t="n">
-        <v>88.28067915000297</v>
+        <v>88.28069493886744</v>
       </c>
       <c r="J8" t="n">
-        <v>68.84358484855829</v>
+        <v>68.84357271248558</v>
       </c>
       <c r="K8" t="n">
-        <v>70.86584987542656</v>
+        <v>70.86586118970865</v>
       </c>
       <c r="L8" t="n">
-        <v>40.92928923749781</v>
+        <v>40.92928618390006</v>
       </c>
       <c r="M8" t="n">
-        <v>32.95975866334893</v>
+        <v>32.95975616494547</v>
       </c>
       <c r="N8" t="n">
-        <v>90.90097123448101</v>
+        <v>90.90098878373759</v>
       </c>
       <c r="O8" t="n">
-        <v>68.22065412583476</v>
+        <v>68.22064257125145</v>
       </c>
       <c r="P8" t="n">
-        <v>29.39524722939154</v>
+        <v>29.39527191510753</v>
       </c>
       <c r="Q8" t="n">
-        <v>24.80058562796385</v>
+        <v>24.80059929466326</v>
       </c>
       <c r="R8" t="n">
-        <v>19.72574003247995</v>
+        <v>19.72574155407388</v>
       </c>
       <c r="S8" t="n">
-        <v>24.9499837142145</v>
+        <v>24.95001087539633</v>
       </c>
     </row>
     <row r="9">
@@ -962,55 +962,55 @@
         <v>198</v>
       </c>
       <c r="C9" t="n">
-        <v>13.53858243094463</v>
+        <v>19.94886587090829</v>
       </c>
       <c r="D9" t="n">
-        <v>19.94886975455354</v>
+        <v>13.53857830953945</v>
       </c>
       <c r="E9" t="n">
-        <v>19.79334586658765</v>
+        <v>19.79336254457878</v>
       </c>
       <c r="F9" t="n">
-        <v>13.79104364450617</v>
+        <v>13.79104580057378</v>
       </c>
       <c r="G9" t="n">
-        <v>11.06749788912401</v>
+        <v>11.06749729064201</v>
       </c>
       <c r="H9" t="n">
-        <v>81.86131109472062</v>
+        <v>81.86131596158255</v>
       </c>
       <c r="I9" t="n">
-        <v>76.57101762824671</v>
+        <v>76.57102295564539</v>
       </c>
       <c r="J9" t="n">
-        <v>69.65906064968068</v>
+        <v>69.65906208439202</v>
       </c>
       <c r="K9" t="n">
-        <v>64.69860884354217</v>
+        <v>64.6986085559701</v>
       </c>
       <c r="L9" t="n">
-        <v>38.88775326841383</v>
+        <v>38.88775070761567</v>
       </c>
       <c r="M9" t="n">
-        <v>32.9747425632743</v>
+        <v>32.97474384132892</v>
       </c>
       <c r="N9" t="n">
-        <v>77.46449582188802</v>
+        <v>77.46450105905109</v>
       </c>
       <c r="O9" t="n">
-        <v>64.9951134089879</v>
+        <v>64.99510818194902</v>
       </c>
       <c r="P9" t="n">
-        <v>14.87168078269686</v>
+        <v>14.87168399312313</v>
       </c>
       <c r="Q9" t="n">
-        <v>15.18215235637979</v>
+        <v>15.18215695745929</v>
       </c>
       <c r="R9" t="n">
-        <v>15.50474641383568</v>
+        <v>15.50475258332362</v>
       </c>
       <c r="S9" t="n">
-        <v>16.08237063069647</v>
+        <v>16.08238313211923</v>
       </c>
     </row>
     <row r="10">
@@ -1023,55 +1023,55 @@
         <v>199</v>
       </c>
       <c r="C10" t="n">
-        <v>8.648750549598715</v>
+        <v>13.53927413668649</v>
       </c>
       <c r="D10" t="n">
-        <v>13.53927791787008</v>
+        <v>8.648755521853689</v>
       </c>
       <c r="E10" t="n">
-        <v>31.64278585734348</v>
+        <v>31.64277675091251</v>
       </c>
       <c r="F10" t="n">
-        <v>12.32221468183018</v>
+        <v>12.32221356486766</v>
       </c>
       <c r="G10" t="n">
-        <v>8.368094194404263</v>
+        <v>8.368094710923323</v>
       </c>
       <c r="H10" t="n">
-        <v>78.86668155715843</v>
+        <v>78.86667915231961</v>
       </c>
       <c r="I10" t="n">
-        <v>76.52015351270474</v>
+        <v>76.52015583082736</v>
       </c>
       <c r="J10" t="n">
-        <v>64.29030086192799</v>
+        <v>64.29029328470416</v>
       </c>
       <c r="K10" t="n">
-        <v>65.91269603148464</v>
+        <v>65.91268694032681</v>
       </c>
       <c r="L10" t="n">
-        <v>33.83621867288022</v>
+        <v>33.83622085034072</v>
       </c>
       <c r="M10" t="n">
-        <v>24.89584368524223</v>
+        <v>24.89584306071376</v>
       </c>
       <c r="N10" t="n">
-        <v>76.41065633240073</v>
+        <v>76.41065398093956</v>
       </c>
       <c r="O10" t="n">
-        <v>63.61515355476919</v>
+        <v>63.61514478929958</v>
       </c>
       <c r="P10" t="n">
-        <v>18.47922709648168</v>
+        <v>18.47923423686532</v>
       </c>
       <c r="Q10" t="n">
-        <v>16.20890733418029</v>
+        <v>16.20891801182428</v>
       </c>
       <c r="R10" t="n">
-        <v>13.86943020882707</v>
+        <v>13.86944472739774</v>
       </c>
       <c r="S10" t="n">
-        <v>16.74683948346444</v>
+        <v>16.74684847977313</v>
       </c>
     </row>
     <row r="11">
@@ -1084,55 +1084,55 @@
         <v>100</v>
       </c>
       <c r="C11" t="n">
-        <v>8.095752223647743</v>
+        <v>16.3675510533527</v>
       </c>
       <c r="D11" t="n">
-        <v>16.36755285866282</v>
+        <v>8.095754928011559</v>
       </c>
       <c r="E11" t="n">
-        <v>20.3547412285939</v>
+        <v>20.35476383125176</v>
       </c>
       <c r="F11" t="n">
-        <v>14.49620798496861</v>
+        <v>14.49621253725341</v>
       </c>
       <c r="G11" t="n">
-        <v>11.53024638631664</v>
+        <v>11.53024689724734</v>
       </c>
       <c r="H11" t="n">
-        <v>83.42530479748528</v>
+        <v>83.42529875245739</v>
       </c>
       <c r="I11" t="n">
-        <v>70.84366772638558</v>
+        <v>70.84368115684508</v>
       </c>
       <c r="J11" t="n">
-        <v>69.03657177332119</v>
+        <v>69.03656959296977</v>
       </c>
       <c r="K11" t="n">
-        <v>64.15642470050918</v>
+        <v>64.15642716867781</v>
       </c>
       <c r="L11" t="n">
-        <v>42.10506080072192</v>
+        <v>42.10506211054349</v>
       </c>
       <c r="M11" t="n">
-        <v>33.14590423163237</v>
+        <v>33.14591178017037</v>
       </c>
       <c r="N11" t="n">
-        <v>75.15461285458244</v>
+        <v>75.15460179904026</v>
       </c>
       <c r="O11" t="n">
-        <v>63.85877223155003</v>
+        <v>63.85876884621573</v>
       </c>
       <c r="P11" t="n">
-        <v>17.24746805212778</v>
+        <v>17.24746467876877</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.66081781397274</v>
+        <v>13.66082176562183</v>
       </c>
       <c r="R11" t="n">
-        <v>9.435605227557232</v>
+        <v>9.43561880204566</v>
       </c>
       <c r="S11" t="n">
-        <v>15.02843679541296</v>
+        <v>15.02842890717294</v>
       </c>
     </row>
     <row r="12">
@@ -1145,55 +1145,55 @@
         <v>106</v>
       </c>
       <c r="C12" t="n">
-        <v>8.374025971314369</v>
+        <v>15.58682746536259</v>
       </c>
       <c r="D12" t="n">
-        <v>15.58682583550753</v>
+        <v>8.374028528913318</v>
       </c>
       <c r="E12" t="n">
-        <v>29.55833107462293</v>
+        <v>29.55833371171079</v>
       </c>
       <c r="F12" t="n">
-        <v>13.59044480876843</v>
+        <v>13.59044517786296</v>
       </c>
       <c r="G12" t="n">
-        <v>9.56977081817176</v>
+        <v>9.56977067327232</v>
       </c>
       <c r="H12" t="n">
-        <v>72.18560468512695</v>
+        <v>72.18559499827657</v>
       </c>
       <c r="I12" t="n">
-        <v>70.8792420946792</v>
+        <v>70.87924090762969</v>
       </c>
       <c r="J12" t="n">
-        <v>55.15241547946721</v>
+        <v>55.15241611288387</v>
       </c>
       <c r="K12" t="n">
-        <v>59.99829425185511</v>
+        <v>59.99828922192868</v>
       </c>
       <c r="L12" t="n">
-        <v>41.26072922875011</v>
+        <v>41.26072896514448</v>
       </c>
       <c r="M12" t="n">
-        <v>31.27321844516247</v>
+        <v>31.27321623522445</v>
       </c>
       <c r="N12" t="n">
-        <v>68.31406392543774</v>
+        <v>68.31406909432286</v>
       </c>
       <c r="O12" t="n">
-        <v>56.13715656226523</v>
+        <v>56.13714988627642</v>
       </c>
       <c r="P12" t="n">
-        <v>23.50274829473471</v>
+        <v>23.50273627176013</v>
       </c>
       <c r="Q12" t="n">
-        <v>19.48732823026583</v>
+        <v>19.48732497229976</v>
       </c>
       <c r="R12" t="n">
-        <v>15.35989515554669</v>
+        <v>15.35990082853262</v>
       </c>
       <c r="S12" t="n">
-        <v>17.81729227398495</v>
+        <v>17.81730849889495</v>
       </c>
     </row>
     <row r="13">
@@ -1206,55 +1206,55 @@
         <v>111</v>
       </c>
       <c r="C13" t="n">
-        <v>7.143700442455832</v>
+        <v>10.68715535854506</v>
       </c>
       <c r="D13" t="n">
-        <v>10.68715826261662</v>
+        <v>7.143692312283047</v>
       </c>
       <c r="E13" t="n">
-        <v>19.89796956403111</v>
+        <v>19.89796348190137</v>
       </c>
       <c r="F13" t="n">
-        <v>14.54035593804842</v>
+        <v>14.54035458699459</v>
       </c>
       <c r="G13" t="n">
-        <v>11.64723326095824</v>
+        <v>11.64723306378975</v>
       </c>
       <c r="H13" t="n">
-        <v>86.83002914036589</v>
+        <v>86.8300153755164</v>
       </c>
       <c r="I13" t="n">
-        <v>81.66118791654007</v>
+        <v>81.66119835324733</v>
       </c>
       <c r="J13" t="n">
-        <v>76.97375145230249</v>
+        <v>76.97374554586054</v>
       </c>
       <c r="K13" t="n">
-        <v>75.03990812855317</v>
+        <v>75.03993762407123</v>
       </c>
       <c r="L13" t="n">
-        <v>37.99164204163046</v>
+        <v>37.99164334611241</v>
       </c>
       <c r="M13" t="n">
-        <v>30.00691487283524</v>
+        <v>30.00692010935741</v>
       </c>
       <c r="N13" t="n">
-        <v>82.57890051096045</v>
+        <v>82.57889024632587</v>
       </c>
       <c r="O13" t="n">
-        <v>74.32779278520427</v>
+        <v>74.32779651833239</v>
       </c>
       <c r="P13" t="n">
-        <v>11.35123914316444</v>
+        <v>11.35123191265648</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.778435343890383</v>
+        <v>9.778419585286841</v>
       </c>
       <c r="R13" t="n">
-        <v>8.105053212426149</v>
+        <v>8.10502877836697</v>
       </c>
       <c r="S13" t="n">
-        <v>9.991759743965158</v>
+        <v>9.991744112615766</v>
       </c>
     </row>
     <row r="14">
@@ -1267,55 +1267,55 @@
         <v>135</v>
       </c>
       <c r="C14" t="n">
-        <v>10.15027314519813</v>
+        <v>17.31906825796492</v>
       </c>
       <c r="D14" t="n">
-        <v>17.31907098145913</v>
+        <v>10.15026639108965</v>
       </c>
       <c r="E14" t="n">
-        <v>26.61905459380887</v>
+        <v>26.61904272407105</v>
       </c>
       <c r="F14" t="n">
-        <v>12.84361838626726</v>
+        <v>12.8436152578368</v>
       </c>
       <c r="G14" t="n">
-        <v>9.393960982373001</v>
+        <v>9.393960206787698</v>
       </c>
       <c r="H14" t="n">
-        <v>77.88112486217682</v>
+        <v>77.88111511648788</v>
       </c>
       <c r="I14" t="n">
-        <v>71.63038406879149</v>
+        <v>71.63038283242088</v>
       </c>
       <c r="J14" t="n">
-        <v>62.79392515172547</v>
+        <v>62.79392253834242</v>
       </c>
       <c r="K14" t="n">
-        <v>59.44957549283106</v>
+        <v>59.44958192586438</v>
       </c>
       <c r="L14" t="n">
-        <v>38.25758740084748</v>
+        <v>38.25758507275935</v>
       </c>
       <c r="M14" t="n">
-        <v>29.12061160727758</v>
+        <v>29.1206125432399</v>
       </c>
       <c r="N14" t="n">
-        <v>72.76823048183201</v>
+        <v>72.76822777410524</v>
       </c>
       <c r="O14" t="n">
-        <v>59.00687454795275</v>
+        <v>59.00687469883086</v>
       </c>
       <c r="P14" t="n">
-        <v>19.33255320848652</v>
+        <v>19.33254714613775</v>
       </c>
       <c r="Q14" t="n">
-        <v>18.22239855165384</v>
+        <v>18.22239030404272</v>
       </c>
       <c r="R14" t="n">
-        <v>17.01817295948292</v>
+        <v>17.01816223934965</v>
       </c>
       <c r="S14" t="n">
-        <v>18.88701724662772</v>
+        <v>18.88701399817691</v>
       </c>
     </row>
     <row r="15">
@@ -1328,55 +1328,55 @@
         <v>990</v>
       </c>
       <c r="C15" t="n">
-        <v>8.801154576936693</v>
+        <v>15.04509395139274</v>
       </c>
       <c r="D15" t="n">
-        <v>15.04509643376934</v>
+        <v>8.801157955363394</v>
       </c>
       <c r="E15" t="n">
-        <v>28.06680949182208</v>
+        <v>28.06681856672202</v>
       </c>
       <c r="F15" t="n">
-        <v>13.70843864430321</v>
+        <v>13.70843744516757</v>
       </c>
       <c r="G15" t="n">
-        <v>9.880882754937753</v>
+        <v>9.880880657355842</v>
       </c>
       <c r="H15" t="n">
-        <v>72.88459280027945</v>
+        <v>72.88458707008357</v>
       </c>
       <c r="I15" t="n">
-        <v>65.60573811408918</v>
+        <v>65.60573541787818</v>
       </c>
       <c r="J15" t="n">
-        <v>54.71591100072548</v>
+        <v>54.7159029903105</v>
       </c>
       <c r="K15" t="n">
-        <v>57.01932162463099</v>
+        <v>57.01930626070236</v>
       </c>
       <c r="L15" t="n">
-        <v>42.353521277448</v>
+        <v>42.35352105852103</v>
       </c>
       <c r="M15" t="n">
-        <v>36.68145424577447</v>
+        <v>36.68145540561881</v>
       </c>
       <c r="N15" t="n">
-        <v>65.96384794300801</v>
+        <v>65.96384157966605</v>
       </c>
       <c r="O15" t="n">
-        <v>53.12108475317694</v>
+        <v>53.12107010766156</v>
       </c>
       <c r="P15" t="n">
-        <v>24.93569049655025</v>
+        <v>24.93569583319484</v>
       </c>
       <c r="Q15" t="n">
-        <v>19.33462617998956</v>
+        <v>19.3346382792861</v>
       </c>
       <c r="R15" t="n">
-        <v>13.09999909743366</v>
+        <v>13.10001891410727</v>
       </c>
       <c r="S15" t="n">
-        <v>19.49172206237021</v>
+        <v>19.49173655393916</v>
       </c>
     </row>
     <row r="16">
@@ -1389,55 +1389,55 @@
         <v>920</v>
       </c>
       <c r="C16" t="n">
-        <v>11.42725892505975</v>
+        <v>18.81916830742378</v>
       </c>
       <c r="D16" t="n">
-        <v>18.81917145805982</v>
+        <v>11.42725276898424</v>
       </c>
       <c r="E16" t="n">
-        <v>29.42505155781111</v>
+        <v>29.42506436431218</v>
       </c>
       <c r="F16" t="n">
-        <v>8.405079719974987</v>
+        <v>8.405080579989153</v>
       </c>
       <c r="G16" t="n">
-        <v>5.923487481468691</v>
+        <v>5.923487022070771</v>
       </c>
       <c r="H16" t="n">
-        <v>69.15528477945581</v>
+        <v>69.15528175416972</v>
       </c>
       <c r="I16" t="n">
-        <v>66.8280499912951</v>
+        <v>66.82806137090058</v>
       </c>
       <c r="J16" t="n">
-        <v>50.65798503336173</v>
+        <v>50.65798633113877</v>
       </c>
       <c r="K16" t="n">
-        <v>50.18133553460968</v>
+        <v>50.18134001331259</v>
       </c>
       <c r="L16" t="n">
-        <v>28.5974756717912</v>
+        <v>28.59747456032087</v>
       </c>
       <c r="M16" t="n">
-        <v>18.10722239072889</v>
+        <v>18.10722147218567</v>
       </c>
       <c r="N16" t="n">
-        <v>67.02469415745666</v>
+        <v>67.02470772865315</v>
       </c>
       <c r="O16" t="n">
-        <v>49.03212488670295</v>
+        <v>49.03212499951399</v>
       </c>
       <c r="P16" t="n">
-        <v>26.74941815016647</v>
+        <v>26.7494129901565</v>
       </c>
       <c r="Q16" t="n">
-        <v>25.84752084856203</v>
+        <v>25.8475211452675</v>
       </c>
       <c r="R16" t="n">
-        <v>24.91067347156953</v>
+        <v>24.91067935499748</v>
       </c>
       <c r="S16" t="n">
-        <v>26.84761140624289</v>
+        <v>26.84762594382292</v>
       </c>
     </row>
   </sheetData>

--- a/2d/results/best_unet_nofilter_projection_mean/best_unet.xlsx
+++ b/2d/results/best_unet_nofilter_projection_mean/best_unet.xlsx
@@ -535,55 +535,55 @@
         <v>140</v>
       </c>
       <c r="C2" t="n">
-        <v>17.1913880048285</v>
+        <v>22.34063605325412</v>
       </c>
       <c r="D2" t="n">
-        <v>10.72350320971258</v>
+        <v>9.894712250161209</v>
       </c>
       <c r="E2" t="n">
-        <v>23.67551765644586</v>
+        <v>20.51806190329523</v>
       </c>
       <c r="F2" t="n">
-        <v>13.06543127443302</v>
+        <v>14.8194322890336</v>
       </c>
       <c r="G2" t="n">
-        <v>9.968000241789925</v>
+        <v>11.78684059374918</v>
       </c>
       <c r="H2" t="n">
-        <v>75.6702603357684</v>
+        <v>83.22075048131188</v>
       </c>
       <c r="I2" t="n">
-        <v>73.45984220576507</v>
+        <v>73.05644899005593</v>
       </c>
       <c r="J2" t="n">
-        <v>62.45796007680266</v>
+        <v>67.39511804192259</v>
       </c>
       <c r="K2" t="n">
-        <v>61.91008622428454</v>
+        <v>64.88532851622865</v>
       </c>
       <c r="L2" t="n">
-        <v>37.75824382840262</v>
+        <v>41.73385332975787</v>
       </c>
       <c r="M2" t="n">
-        <v>29.31709498830734</v>
+        <v>34.15121268059561</v>
       </c>
       <c r="N2" t="n">
-        <v>72.13506012522207</v>
+        <v>75.64173074246199</v>
       </c>
       <c r="O2" t="n">
-        <v>59.73434710318713</v>
+        <v>63.2403873276495</v>
       </c>
       <c r="P2" t="n">
-        <v>17.42470085273971</v>
+        <v>19.00225667751262</v>
       </c>
       <c r="Q2" t="n">
-        <v>16.59393930612883</v>
+        <v>15.3456475445316</v>
       </c>
       <c r="R2" t="n">
-        <v>15.72736227004281</v>
+        <v>11.1726504842392</v>
       </c>
       <c r="S2" t="n">
-        <v>17.1706454952099</v>
+        <v>16.3790400575455</v>
       </c>
     </row>
     <row r="3">
@@ -596,55 +596,55 @@
         <v>141</v>
       </c>
       <c r="C3" t="n">
-        <v>12.37436192103275</v>
+        <v>18.06221206130949</v>
       </c>
       <c r="D3" t="n">
-        <v>6.39121034849195</v>
+        <v>6.883387858156311</v>
       </c>
       <c r="E3" t="n">
-        <v>25.27682963516356</v>
+        <v>26.06138173303135</v>
       </c>
       <c r="F3" t="n">
-        <v>21.1550117547425</v>
+        <v>25.15083145814204</v>
       </c>
       <c r="G3" t="n">
-        <v>15.80365461591601</v>
+        <v>18.58285045979542</v>
       </c>
       <c r="H3" t="n">
-        <v>81.37442592849129</v>
+        <v>94.19870072275123</v>
       </c>
       <c r="I3" t="n">
-        <v>88.02658995922096</v>
+        <v>90.60265927108954</v>
       </c>
       <c r="J3" t="n">
-        <v>70.50998324251277</v>
+        <v>77.98077973060472</v>
       </c>
       <c r="K3" t="n">
-        <v>76.93915156275423</v>
+        <v>79.46877653142101</v>
       </c>
       <c r="L3" t="n">
-        <v>53.61703105952269</v>
+        <v>59.76558204406022</v>
       </c>
       <c r="M3" t="n">
-        <v>44.10075824345201</v>
+        <v>47.97360781663535</v>
       </c>
       <c r="N3" t="n">
-        <v>80.46903373757819</v>
+        <v>87.59000473880276</v>
       </c>
       <c r="O3" t="n">
-        <v>70.48574316789333</v>
+        <v>75.49244762517891</v>
       </c>
       <c r="P3" t="n">
-        <v>13.35022323333284</v>
+        <v>17.22254939851623</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.96207614962903</v>
+        <v>14.80613151794926</v>
       </c>
       <c r="R3" t="n">
-        <v>12.59683606381701</v>
+        <v>12.28664379889174</v>
       </c>
       <c r="S3" t="n">
-        <v>12.41114498237569</v>
+        <v>13.82740007011682</v>
       </c>
     </row>
     <row r="4">
@@ -657,55 +657,55 @@
         <v>149</v>
       </c>
       <c r="C4" t="n">
-        <v>9.408123224513668</v>
+        <v>11.03367510228076</v>
       </c>
       <c r="D4" t="n">
-        <v>7.999021292500264</v>
+        <v>11.94483392141039</v>
       </c>
       <c r="E4" t="n">
-        <v>17.04209245603023</v>
+        <v>19.03622360026512</v>
       </c>
       <c r="F4" t="n">
-        <v>11.1381249721468</v>
+        <v>13.45548957120301</v>
       </c>
       <c r="G4" t="n">
-        <v>9.240034732448599</v>
+        <v>10.88839377209246</v>
       </c>
       <c r="H4" t="n">
-        <v>82.9899126568486</v>
+        <v>88.2996337644272</v>
       </c>
       <c r="I4" t="n">
-        <v>74.41229767416432</v>
+        <v>73.98925281426968</v>
       </c>
       <c r="J4" t="n">
-        <v>71.41829996058893</v>
+        <v>76.41300796763721</v>
       </c>
       <c r="K4" t="n">
-        <v>63.24876618357676</v>
+        <v>59.71546975798355</v>
       </c>
       <c r="L4" t="n">
-        <v>33.29506958996561</v>
+        <v>39.23310642581103</v>
       </c>
       <c r="M4" t="n">
-        <v>26.89594004564418</v>
+        <v>33.3251570644204</v>
       </c>
       <c r="N4" t="n">
-        <v>77.43168118873314</v>
+        <v>79.33629862030885</v>
       </c>
       <c r="O4" t="n">
-        <v>65.93784011197602</v>
+        <v>65.94263286478491</v>
       </c>
       <c r="P4" t="n">
-        <v>13.93797354934514</v>
+        <v>13.46090030041359</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.43901475691114</v>
+        <v>16.11743940502906</v>
       </c>
       <c r="R4" t="n">
-        <v>15.00421505810901</v>
+        <v>19.28522820268452</v>
       </c>
       <c r="S4" t="n">
-        <v>14.84276964400785</v>
+        <v>16.87531438868603</v>
       </c>
     </row>
     <row r="5">
@@ -718,55 +718,55 @@
         <v>160</v>
       </c>
       <c r="C5" t="n">
-        <v>15.9012155646825</v>
+        <v>17.30910010487222</v>
       </c>
       <c r="D5" t="n">
-        <v>11.51883286635027</v>
+        <v>9.72859342069223</v>
       </c>
       <c r="E5" t="n">
-        <v>33.21206386674271</v>
+        <v>20.37489257448257</v>
       </c>
       <c r="F5" t="n">
-        <v>10.94531196145207</v>
+        <v>13.87692522309866</v>
       </c>
       <c r="G5" t="n">
-        <v>7.309735806694785</v>
+        <v>11.06217829105961</v>
       </c>
       <c r="H5" t="n">
-        <v>68.24729665178604</v>
+        <v>78.93828610856713</v>
       </c>
       <c r="I5" t="n">
-        <v>67.40729494083915</v>
+        <v>71.04977333884904</v>
       </c>
       <c r="J5" t="n">
-        <v>53.69306056156531</v>
+        <v>64.04013809481994</v>
       </c>
       <c r="K5" t="n">
-        <v>51.74052789194971</v>
+        <v>57.79026529599314</v>
       </c>
       <c r="L5" t="n">
-        <v>35.37432263664697</v>
+        <v>42.5872699543436</v>
       </c>
       <c r="M5" t="n">
-        <v>28.11253471873947</v>
+        <v>34.65991764271348</v>
       </c>
       <c r="N5" t="n">
-        <v>65.69060219892286</v>
+        <v>72.5165348768449</v>
       </c>
       <c r="O5" t="n">
-        <v>50.71336807284813</v>
+        <v>58.02539592034103</v>
       </c>
       <c r="P5" t="n">
-        <v>21.28817285813567</v>
+        <v>18.85712689403769</v>
       </c>
       <c r="Q5" t="n">
-        <v>22.26543173992862</v>
+        <v>18.77867795989376</v>
       </c>
       <c r="R5" t="n">
-        <v>23.24623892697194</v>
+        <v>18.67572438744563</v>
       </c>
       <c r="S5" t="n">
-        <v>22.77961038272962</v>
+        <v>19.98415775119726</v>
       </c>
     </row>
     <row r="6">
@@ -779,55 +779,55 @@
         <v>170</v>
       </c>
       <c r="C6" t="n">
-        <v>14.59153886933953</v>
+        <v>15.0464786887991</v>
       </c>
       <c r="D6" t="n">
-        <v>8.837936138548233</v>
+        <v>12.95162312926364</v>
       </c>
       <c r="E6" t="n">
-        <v>23.95294242439894</v>
+        <v>21.58872417975207</v>
       </c>
       <c r="F6" t="n">
-        <v>14.84331724861455</v>
+        <v>17.72049381010595</v>
       </c>
       <c r="G6" t="n">
-        <v>11.28333873067911</v>
+        <v>13.89392908600137</v>
       </c>
       <c r="H6" t="n">
-        <v>80.03329544047475</v>
+        <v>91.10634800334135</v>
       </c>
       <c r="I6" t="n">
-        <v>75.55599936287534</v>
+        <v>77.81450410826032</v>
       </c>
       <c r="J6" t="n">
-        <v>57.02504921161473</v>
+        <v>61.61885455990171</v>
       </c>
       <c r="K6" t="n">
-        <v>61.74427003876174</v>
+        <v>59.44175641348843</v>
       </c>
       <c r="L6" t="n">
-        <v>42.41043470816869</v>
+        <v>53.015288744328</v>
       </c>
       <c r="M6" t="n">
-        <v>37.10194994405313</v>
+        <v>43.37018062730817</v>
       </c>
       <c r="N6" t="n">
-        <v>74.81926628599307</v>
+        <v>81.23697999771763</v>
       </c>
       <c r="O6" t="n">
-        <v>55.83459187601648</v>
+        <v>55.19401691361934</v>
       </c>
       <c r="P6" t="n">
-        <v>28.7515645233392</v>
+        <v>32.357039778477</v>
       </c>
       <c r="Q6" t="n">
-        <v>23.66679705792902</v>
+        <v>28.33134587416156</v>
       </c>
       <c r="R6" t="n">
-        <v>18.28049657379685</v>
+        <v>23.55945350829412</v>
       </c>
       <c r="S6" t="n">
-        <v>25.37196114117926</v>
+        <v>32.05826942180757</v>
       </c>
     </row>
     <row r="7">
@@ -840,55 +840,55 @@
         <v>184</v>
       </c>
       <c r="C7" t="n">
-        <v>12.34960640984924</v>
+        <v>12.19159855513363</v>
       </c>
       <c r="D7" t="n">
-        <v>10.19025612983872</v>
+        <v>11.22776448183934</v>
       </c>
       <c r="E7" t="n">
-        <v>25.63177835798014</v>
+        <v>30.12048149356417</v>
       </c>
       <c r="F7" t="n">
-        <v>12.52307031037853</v>
+        <v>15.1019401904443</v>
       </c>
       <c r="G7" t="n">
-        <v>9.312788848645738</v>
+        <v>10.56236732834377</v>
       </c>
       <c r="H7" t="n">
-        <v>77.58726735950572</v>
+        <v>83.09047824897533</v>
       </c>
       <c r="I7" t="n">
-        <v>73.94793078992159</v>
+        <v>73.9347989535573</v>
       </c>
       <c r="J7" t="n">
-        <v>65.37255970879188</v>
+        <v>70.91034533640122</v>
       </c>
       <c r="K7" t="n">
-        <v>62.56229207113487</v>
+        <v>63.23364945946798</v>
       </c>
       <c r="L7" t="n">
-        <v>35.04506141651712</v>
+        <v>42.27077449799405</v>
       </c>
       <c r="M7" t="n">
-        <v>28.27914684212428</v>
+        <v>31.79263728881627</v>
       </c>
       <c r="N7" t="n">
-        <v>73.36882814481218</v>
+        <v>74.95491205817864</v>
       </c>
       <c r="O7" t="n">
-        <v>62.5605882042253</v>
+        <v>66.43103641851705</v>
       </c>
       <c r="P7" t="n">
-        <v>15.6303887171547</v>
+        <v>14.55199646325308</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.53419022595013</v>
+        <v>14.50644449501882</v>
       </c>
       <c r="R7" t="n">
-        <v>15.40457705660049</v>
+        <v>14.47530717726079</v>
       </c>
       <c r="S7" t="n">
-        <v>14.68329486124664</v>
+        <v>11.31243157369916</v>
       </c>
     </row>
     <row r="8">
@@ -901,55 +901,55 @@
         <v>190</v>
       </c>
       <c r="C8" t="n">
-        <v>11.50388386090963</v>
+        <v>13.59632880290153</v>
       </c>
       <c r="D8" t="n">
-        <v>4.884867107617458</v>
+        <v>6.25838516638283</v>
       </c>
       <c r="E8" t="n">
-        <v>34.40661891430317</v>
+        <v>22.48453519341831</v>
       </c>
       <c r="F8" t="n">
-        <v>17.37308260205274</v>
+        <v>20.02933521700069</v>
       </c>
       <c r="G8" t="n">
-        <v>11.39555018900475</v>
+        <v>15.52324536683739</v>
       </c>
       <c r="H8" t="n">
-        <v>97.50697397206069</v>
+        <v>101.1053633858172</v>
       </c>
       <c r="I8" t="n">
-        <v>88.28069493886744</v>
+        <v>85.85767318580841</v>
       </c>
       <c r="J8" t="n">
-        <v>68.84357271248558</v>
+        <v>82.38741637252141</v>
       </c>
       <c r="K8" t="n">
-        <v>70.86586118970865</v>
+        <v>76.18312809048261</v>
       </c>
       <c r="L8" t="n">
-        <v>40.92928618390006</v>
+        <v>47.43929868618391</v>
       </c>
       <c r="M8" t="n">
-        <v>32.95975616494547</v>
+        <v>40.4602127959453</v>
       </c>
       <c r="N8" t="n">
-        <v>90.90098878373759</v>
+        <v>91.08717643280636</v>
       </c>
       <c r="O8" t="n">
-        <v>68.22064257125145</v>
+        <v>76.66438166083651</v>
       </c>
       <c r="P8" t="n">
-        <v>29.39527191510753</v>
+        <v>18.51337865109148</v>
       </c>
       <c r="Q8" t="n">
-        <v>24.80059929466326</v>
+        <v>15.18570276233308</v>
       </c>
       <c r="R8" t="n">
-        <v>19.72574155407388</v>
+        <v>11.26608881295065</v>
       </c>
       <c r="S8" t="n">
-        <v>24.95001087539633</v>
+        <v>15.83375445250914</v>
       </c>
     </row>
     <row r="9">
@@ -962,55 +962,55 @@
         <v>198</v>
       </c>
       <c r="C9" t="n">
-        <v>19.94886587090829</v>
+        <v>20.68463805831352</v>
       </c>
       <c r="D9" t="n">
-        <v>13.53857830953945</v>
+        <v>12.75297469905731</v>
       </c>
       <c r="E9" t="n">
-        <v>19.79336254457878</v>
+        <v>15.32710769455485</v>
       </c>
       <c r="F9" t="n">
-        <v>13.79104580057378</v>
+        <v>16.16843722564453</v>
       </c>
       <c r="G9" t="n">
-        <v>11.06749729064201</v>
+        <v>13.68492784551036</v>
       </c>
       <c r="H9" t="n">
-        <v>81.86131596158255</v>
+        <v>90.47552802259956</v>
       </c>
       <c r="I9" t="n">
-        <v>76.57102295564539</v>
+        <v>79.71422287813495</v>
       </c>
       <c r="J9" t="n">
-        <v>69.65906208439202</v>
+        <v>73.67625677151139</v>
       </c>
       <c r="K9" t="n">
-        <v>64.6986085559701</v>
+        <v>67.63481816687674</v>
       </c>
       <c r="L9" t="n">
-        <v>38.88775070761567</v>
+        <v>44.04072323259839</v>
       </c>
       <c r="M9" t="n">
-        <v>32.97474384132892</v>
+        <v>37.07608320922784</v>
       </c>
       <c r="N9" t="n">
-        <v>77.46450105905109</v>
+        <v>82.98082907318764</v>
       </c>
       <c r="O9" t="n">
-        <v>64.99510818194902</v>
+        <v>68.01930555742804</v>
       </c>
       <c r="P9" t="n">
-        <v>14.87168399312313</v>
+        <v>18.47176337279306</v>
       </c>
       <c r="Q9" t="n">
-        <v>15.18215695745929</v>
+        <v>16.92987749613071</v>
       </c>
       <c r="R9" t="n">
-        <v>15.50475258332362</v>
+        <v>15.14876348956559</v>
       </c>
       <c r="S9" t="n">
-        <v>16.08238313211923</v>
+        <v>18.00457305237964</v>
       </c>
     </row>
     <row r="10">
@@ -1023,55 +1023,55 @@
         <v>199</v>
       </c>
       <c r="C10" t="n">
-        <v>13.53927413668649</v>
+        <v>16.44289723904234</v>
       </c>
       <c r="D10" t="n">
-        <v>8.648755521853689</v>
+        <v>10.29700841566054</v>
       </c>
       <c r="E10" t="n">
-        <v>31.64277675091251</v>
+        <v>26.27731882815725</v>
       </c>
       <c r="F10" t="n">
-        <v>12.32221356486766</v>
+        <v>14.62957461681319</v>
       </c>
       <c r="G10" t="n">
-        <v>8.368094710923323</v>
+        <v>10.76361209844106</v>
       </c>
       <c r="H10" t="n">
-        <v>78.86667915231961</v>
+        <v>89.80990684316127</v>
       </c>
       <c r="I10" t="n">
-        <v>76.52015583082736</v>
+        <v>81.79878206965078</v>
       </c>
       <c r="J10" t="n">
-        <v>64.29029328470416</v>
+        <v>75.45915520991123</v>
       </c>
       <c r="K10" t="n">
-        <v>65.91268694032681</v>
+        <v>70.53664345361057</v>
       </c>
       <c r="L10" t="n">
-        <v>33.83622085034072</v>
+        <v>38.27355348097792</v>
       </c>
       <c r="M10" t="n">
-        <v>24.89584306071376</v>
+        <v>27.83812980604954</v>
       </c>
       <c r="N10" t="n">
-        <v>76.41065398093956</v>
+        <v>84.07304602763618</v>
       </c>
       <c r="O10" t="n">
-        <v>63.61514478929958</v>
+        <v>71.61571182724113</v>
       </c>
       <c r="P10" t="n">
-        <v>18.47923423686532</v>
+        <v>15.97249461954085</v>
       </c>
       <c r="Q10" t="n">
-        <v>16.20891801182428</v>
+        <v>14.92260144710365</v>
       </c>
       <c r="R10" t="n">
-        <v>13.86944472739774</v>
+        <v>13.76871511301925</v>
       </c>
       <c r="S10" t="n">
-        <v>16.74684847977313</v>
+        <v>14.81177282509094</v>
       </c>
     </row>
     <row r="11">
@@ -1084,55 +1084,55 @@
         <v>100</v>
       </c>
       <c r="C11" t="n">
-        <v>16.3675510533527</v>
+        <v>16.88054494114751</v>
       </c>
       <c r="D11" t="n">
-        <v>8.095754928011559</v>
+        <v>10.9108608969174</v>
       </c>
       <c r="E11" t="n">
-        <v>20.35476383125176</v>
+        <v>18.08036324939508</v>
       </c>
       <c r="F11" t="n">
-        <v>14.49621253725341</v>
+        <v>19.31155010151029</v>
       </c>
       <c r="G11" t="n">
-        <v>11.53024689724734</v>
+        <v>15.81801636561335</v>
       </c>
       <c r="H11" t="n">
-        <v>83.42529875245739</v>
+        <v>102.4316483266396</v>
       </c>
       <c r="I11" t="n">
-        <v>70.84368115684508</v>
+        <v>82.25290409690669</v>
       </c>
       <c r="J11" t="n">
-        <v>69.03656959296977</v>
+        <v>87.3261343957895</v>
       </c>
       <c r="K11" t="n">
-        <v>64.15642716867781</v>
+        <v>70.07996508714695</v>
       </c>
       <c r="L11" t="n">
-        <v>42.10506211054349</v>
+        <v>51.66248470600274</v>
       </c>
       <c r="M11" t="n">
-        <v>33.14591178017037</v>
+        <v>40.75165455965123</v>
       </c>
       <c r="N11" t="n">
-        <v>75.15460179904026</v>
+        <v>90.23513976908158</v>
       </c>
       <c r="O11" t="n">
-        <v>63.85876884621573</v>
+        <v>75.48954844762832</v>
       </c>
       <c r="P11" t="n">
-        <v>17.24746467876877</v>
+        <v>14.7432277907413</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.66082176562183</v>
+        <v>14.77132935358408</v>
       </c>
       <c r="R11" t="n">
-        <v>9.43561880204566</v>
+        <v>14.80259177661076</v>
       </c>
       <c r="S11" t="n">
-        <v>15.02842890717294</v>
+        <v>16.34497873788528</v>
       </c>
     </row>
     <row r="12">
@@ -1145,55 +1145,55 @@
         <v>106</v>
       </c>
       <c r="C12" t="n">
-        <v>15.58682746536259</v>
+        <v>23.3168497400356</v>
       </c>
       <c r="D12" t="n">
-        <v>8.374028528913318</v>
+        <v>14.78911802088916</v>
       </c>
       <c r="E12" t="n">
-        <v>29.55833371171079</v>
+        <v>36.43496932727518</v>
       </c>
       <c r="F12" t="n">
-        <v>13.59044517786296</v>
+        <v>14.46582393594998</v>
       </c>
       <c r="G12" t="n">
-        <v>9.56977067327232</v>
+        <v>9.192602057270344</v>
       </c>
       <c r="H12" t="n">
-        <v>72.18559499827657</v>
+        <v>78.9111274962579</v>
       </c>
       <c r="I12" t="n">
-        <v>70.87924090762969</v>
+        <v>72.94893724247275</v>
       </c>
       <c r="J12" t="n">
-        <v>55.15241611288387</v>
+        <v>52.49686354372146</v>
       </c>
       <c r="K12" t="n">
-        <v>59.99828922192868</v>
+        <v>58.19402630538837</v>
       </c>
       <c r="L12" t="n">
-        <v>41.26072896514448</v>
+        <v>43.29796116912643</v>
       </c>
       <c r="M12" t="n">
-        <v>31.27321623522445</v>
+        <v>32.85685588551576</v>
       </c>
       <c r="N12" t="n">
-        <v>68.31406909432286</v>
+        <v>71.47487205277656</v>
       </c>
       <c r="O12" t="n">
-        <v>56.13714988627642</v>
+        <v>54.48056927231545</v>
       </c>
       <c r="P12" t="n">
-        <v>23.50273627176013</v>
+        <v>33.47084459137758</v>
       </c>
       <c r="Q12" t="n">
-        <v>19.48732497229976</v>
+        <v>27.09163148621677</v>
       </c>
       <c r="R12" t="n">
-        <v>15.35990082853262</v>
+        <v>20.17415386131021</v>
       </c>
       <c r="S12" t="n">
-        <v>17.81730849889495</v>
+        <v>23.77564292261025</v>
       </c>
     </row>
     <row r="13">
@@ -1206,55 +1206,55 @@
         <v>111</v>
       </c>
       <c r="C13" t="n">
-        <v>10.68715535854506</v>
+        <v>9.878275453324232</v>
       </c>
       <c r="D13" t="n">
-        <v>7.143692312283047</v>
+        <v>6.5457695173535</v>
       </c>
       <c r="E13" t="n">
-        <v>19.89796348190137</v>
+        <v>19.2275612714062</v>
       </c>
       <c r="F13" t="n">
-        <v>14.54035458699459</v>
+        <v>18.34005829922938</v>
       </c>
       <c r="G13" t="n">
-        <v>11.64723306378975</v>
+        <v>14.81371397879498</v>
       </c>
       <c r="H13" t="n">
-        <v>86.8300153755164</v>
+        <v>91.78062951378675</v>
       </c>
       <c r="I13" t="n">
-        <v>81.66119835324733</v>
+        <v>80.12411262241663</v>
       </c>
       <c r="J13" t="n">
-        <v>76.97374554586054</v>
+        <v>84.35325257051502</v>
       </c>
       <c r="K13" t="n">
-        <v>75.03993762407123</v>
+        <v>72.77780059275939</v>
       </c>
       <c r="L13" t="n">
-        <v>37.99164334611241</v>
+        <v>47.03230704221926</v>
       </c>
       <c r="M13" t="n">
-        <v>30.00692010935741</v>
+        <v>39.4856425559263</v>
       </c>
       <c r="N13" t="n">
-        <v>82.57889024632587</v>
+        <v>83.23480987230948</v>
       </c>
       <c r="O13" t="n">
-        <v>74.32779651833239</v>
+        <v>76.28810646300015</v>
       </c>
       <c r="P13" t="n">
-        <v>11.35123191265648</v>
+        <v>8.092647100172181</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.778419585286841</v>
+        <v>8.592267616344623</v>
       </c>
       <c r="R13" t="n">
-        <v>8.10502877836697</v>
+        <v>9.157533266418607</v>
       </c>
       <c r="S13" t="n">
-        <v>9.991744112615766</v>
+        <v>8.346067550604763</v>
       </c>
     </row>
     <row r="14">
@@ -1267,55 +1267,55 @@
         <v>135</v>
       </c>
       <c r="C14" t="n">
-        <v>17.31906825796492</v>
+        <v>19.20567391896668</v>
       </c>
       <c r="D14" t="n">
-        <v>10.15026639108965</v>
+        <v>10.99903527147132</v>
       </c>
       <c r="E14" t="n">
-        <v>26.61904272407105</v>
+        <v>32.09449353331298</v>
       </c>
       <c r="F14" t="n">
-        <v>12.8436152578368</v>
+        <v>17.79790147215492</v>
       </c>
       <c r="G14" t="n">
-        <v>9.393960206787698</v>
+        <v>12.11026056706453</v>
       </c>
       <c r="H14" t="n">
-        <v>77.88111511648788</v>
+        <v>87.29745593723727</v>
       </c>
       <c r="I14" t="n">
-        <v>71.63038283242088</v>
+        <v>77.78785743509782</v>
       </c>
       <c r="J14" t="n">
-        <v>62.79392253834242</v>
+        <v>68.5161726243457</v>
       </c>
       <c r="K14" t="n">
-        <v>59.44958192586438</v>
+        <v>62.49352392164908</v>
       </c>
       <c r="L14" t="n">
-        <v>38.25758507275935</v>
+        <v>51.29758045675336</v>
       </c>
       <c r="M14" t="n">
-        <v>29.1206125432399</v>
+        <v>35.78427180655981</v>
       </c>
       <c r="N14" t="n">
-        <v>72.76822777410524</v>
+        <v>77.94916068655209</v>
       </c>
       <c r="O14" t="n">
-        <v>59.00687469883086</v>
+        <v>63.34992796273794</v>
       </c>
       <c r="P14" t="n">
-        <v>19.33254714613775</v>
+        <v>21.49244699689808</v>
       </c>
       <c r="Q14" t="n">
-        <v>18.22239030404272</v>
+        <v>20.65522468305336</v>
       </c>
       <c r="R14" t="n">
-        <v>17.01816223934965</v>
+        <v>19.68721068576457</v>
       </c>
       <c r="S14" t="n">
-        <v>18.88701399817691</v>
+        <v>18.74177521559436</v>
       </c>
     </row>
     <row r="15">
@@ -1328,55 +1328,55 @@
         <v>990</v>
       </c>
       <c r="C15" t="n">
-        <v>15.04509395139274</v>
+        <v>11.78388948925103</v>
       </c>
       <c r="D15" t="n">
-        <v>8.801157955363394</v>
+        <v>7.975707507227726</v>
       </c>
       <c r="E15" t="n">
-        <v>28.06681856672202</v>
+        <v>31.0007562435412</v>
       </c>
       <c r="F15" t="n">
-        <v>13.70843744516757</v>
+        <v>14.76146172767852</v>
       </c>
       <c r="G15" t="n">
-        <v>9.880880657355842</v>
+        <v>10.19678931238499</v>
       </c>
       <c r="H15" t="n">
-        <v>72.88458707008357</v>
+        <v>77.89207618498588</v>
       </c>
       <c r="I15" t="n">
-        <v>65.60573541787818</v>
+        <v>65.65535017136642</v>
       </c>
       <c r="J15" t="n">
-        <v>54.7159029903105</v>
+        <v>61.18576117503754</v>
       </c>
       <c r="K15" t="n">
-        <v>57.01930626070236</v>
+        <v>52.71230860339108</v>
       </c>
       <c r="L15" t="n">
-        <v>42.35352105852103</v>
+        <v>47.95732759323849</v>
       </c>
       <c r="M15" t="n">
-        <v>36.68145540561881</v>
+        <v>38.67029906017805</v>
       </c>
       <c r="N15" t="n">
-        <v>65.96384157966605</v>
+        <v>67.27287399215936</v>
       </c>
       <c r="O15" t="n">
-        <v>53.12107010766156</v>
+        <v>54.29659799106351</v>
       </c>
       <c r="P15" t="n">
-        <v>24.93569583319484</v>
+        <v>21.48305476983674</v>
       </c>
       <c r="Q15" t="n">
-        <v>19.3346382792861</v>
+        <v>20.69507151777875</v>
       </c>
       <c r="R15" t="n">
-        <v>13.10001891410727</v>
+        <v>19.75570089375687</v>
       </c>
       <c r="S15" t="n">
-        <v>19.49173655393916</v>
+        <v>19.34275920993601</v>
       </c>
     </row>
     <row r="16">
@@ -1389,55 +1389,55 @@
         <v>920</v>
       </c>
       <c r="C16" t="n">
-        <v>18.81916830742378</v>
+        <v>22.66106259828474</v>
       </c>
       <c r="D16" t="n">
-        <v>11.42725276898424</v>
+        <v>11.02958985184228</v>
       </c>
       <c r="E16" t="n">
-        <v>29.42506436431218</v>
+        <v>25.25811102493394</v>
       </c>
       <c r="F16" t="n">
-        <v>8.405080579989153</v>
+        <v>12.07808820401624</v>
       </c>
       <c r="G16" t="n">
-        <v>5.923487022070771</v>
+        <v>9.015272293231392</v>
       </c>
       <c r="H16" t="n">
-        <v>69.15528175416972</v>
+        <v>84.55573442841359</v>
       </c>
       <c r="I16" t="n">
-        <v>66.82806137090058</v>
+        <v>77.39836493689634</v>
       </c>
       <c r="J16" t="n">
-        <v>50.65798633113877</v>
+        <v>55.49790989243541</v>
       </c>
       <c r="K16" t="n">
-        <v>50.18134001331259</v>
+        <v>53.75663525145666</v>
       </c>
       <c r="L16" t="n">
-        <v>28.59747456032087</v>
+        <v>36.16468703070483</v>
       </c>
       <c r="M16" t="n">
-        <v>18.10722147218567</v>
+        <v>27.73690296038215</v>
       </c>
       <c r="N16" t="n">
-        <v>67.02470772865315</v>
+        <v>79.39751199411928</v>
       </c>
       <c r="O16" t="n">
-        <v>49.03212499951399</v>
+        <v>51.99773140929565</v>
       </c>
       <c r="P16" t="n">
-        <v>26.7494129901565</v>
+        <v>34.4019981202647</v>
       </c>
       <c r="Q16" t="n">
-        <v>25.8475211452675</v>
+        <v>32.58979083121999</v>
       </c>
       <c r="R16" t="n">
-        <v>24.91067935499748</v>
+        <v>30.56031247930716</v>
       </c>
       <c r="S16" t="n">
-        <v>26.84762594382292</v>
+        <v>34.55465388640464</v>
       </c>
     </row>
   </sheetData>
